--- a/doc/examples/resource/resource-efficiency.xlsx
+++ b/doc/examples/resource/resource-efficiency.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\johan\workspace\frepple-community\doc\examples\resource\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\jdetaeye\workspace\frepple-community\doc\examples\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B39D5CB-BE7B-4C98-BA6E-9FA5CFFB9733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E23FF5B-7B7D-43A1-956B-9C167EADF1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="-15720" windowWidth="27885" windowHeight="12225" tabRatio="821" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="2280" windowWidth="38355" windowHeight="12015" tabRatio="821" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sales order" sheetId="1" r:id="rId1"/>
@@ -108,9 +108,6 @@
     <t>All items</t>
   </si>
   <si>
-    <t>grinded wooden panel</t>
-  </si>
-  <si>
     <t>raw material</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>old machine</t>
   </si>
   <si>
-    <t>grinded wooden panel supplier</t>
-  </si>
-  <si>
     <t>screw supplier</t>
   </si>
   <si>
@@ -301,6 +295,12 @@
   </si>
   <si>
     <t>Minshipment</t>
+  </si>
+  <si>
+    <t>polished wooden panel</t>
+  </si>
+  <si>
+    <t>polished wooden panel supplier</t>
   </si>
 </sst>
 </file>
@@ -657,16 +657,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" customWidth="1"/>
+    <col min="2" max="2" width="17.6328125" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,13 +689,13 @@
         <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -762,41 +762,41 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -811,140 +811,140 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="136.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="136.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>63</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>65</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>66</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>69</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>74</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>76</v>
       </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="C10" t="s">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>79</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -956,12 +956,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -978,29 +978,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
       </c>
       <c r="E3">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1008,33 +1008,33 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1042,27 +1042,27 @@
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1077,9 +1077,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1087,17 +1087,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1109,14 +1109,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1130,12 +1130,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,35 +1143,35 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
       <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1180,15 +1180,15 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1206,29 +1206,29 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1240,9 +1240,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -1250,30 +1250,30 @@
         <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2">
         <v>3000</v>
@@ -1285,15 +1285,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1302,15 +1302,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1328,27 +1328,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1366,30 +1366,30 @@
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
@@ -1413,18 +1413,18 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -1457,18 +1457,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -1477,15 +1477,15 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -1494,12 +1494,12 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -1508,91 +1508,91 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>-1</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>-1</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>-5</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>-10</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
